--- a/oranlar_yaklasan.xlsx
+++ b/oranlar_yaklasan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA59"/>
+  <dimension ref="A1:BA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,7 +685,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4504380</v>
+        <v>4522604</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -694,77 +694,93 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ELSAL</t>
+          <t>SUUD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Deportivo Fas</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Isidro Metapan</t>
+          <t>Al Shabab (Riya</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>3.19</v>
       </c>
       <c r="I2" t="n">
-        <v>2.85</v>
+        <v>1.84</v>
       </c>
       <c r="J2" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="K2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>1.35</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="U2" t="n">
-        <v>3.38</v>
+        <v>2.31</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="X2" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>1.95</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.04</v>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -792,7 +808,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4476467</v>
+        <v>4537788</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -801,93 +817,73 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MEK</t>
+          <t>MLTP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pumas Unam</t>
+          <t>Birkirkara</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="H3" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>2.57</v>
+        <v>1.78</v>
       </c>
       <c r="J3" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="K3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="M3" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="N3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>8.94</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.21</v>
-      </c>
+        <v>1.63</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -915,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4476466</v>
+        <v>4484982</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -924,93 +920,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MEK</t>
+          <t>KARA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Buducnost</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Fk Arsenal Tiva</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.37</v>
       </c>
       <c r="I4" t="n">
-        <v>1.93</v>
+        <v>5.02</v>
       </c>
       <c r="J4" t="n">
-        <v>1.37</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="N4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9.890000000000001</v>
-      </c>
+        <v>1.69</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>3.07</v>
+        <v>1.83</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>5.37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.32</v>
-      </c>
+        <v>2.39</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1038,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4550370</v>
+        <v>4450290</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1047,72 +1027,68 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ENDL1</t>
+          <t>EST2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persik</t>
+          <t xml:space="preserve">Flora Tallinn </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pss Sleman</t>
+          <t>Nomme United Ii</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="I5" t="n">
-        <v>3.42</v>
+        <v>2.64</v>
       </c>
       <c r="J5" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="K5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.54</v>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="U5" t="n">
-        <v>3.87</v>
+        <v>2.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.79</v>
+        <v>3.3</v>
       </c>
       <c r="X5" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1145,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4550369</v>
+        <v>4549594</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1154,77 +1130,93 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ENDL1</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Psm Makassar</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persebaya</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3.04</v>
+        <v>1.37</v>
       </c>
       <c r="H6" t="n">
-        <v>2.97</v>
+        <v>3.87</v>
       </c>
       <c r="I6" t="n">
-        <v>1.76</v>
+        <v>5.01</v>
       </c>
       <c r="J6" t="n">
-        <v>1.47</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.12</v>
+        <v>2.12</v>
       </c>
       <c r="M6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.6</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.53</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+        <v>2.19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.43</v>
+      </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1252,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4550371</v>
+        <v>4549550</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1261,77 +1253,93 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ENDL1</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3.79</v>
+        <v>1.17</v>
       </c>
       <c r="H7" t="n">
-        <v>3.18</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.53</v>
+        <v>7.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.93</v>
+      </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1359,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4484978</v>
+        <v>4549665</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1368,77 +1376,93 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KARA</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mornar Bar</t>
+          <t>Fc Iberia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mladost Dg</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R8" t="n">
+        <v>14</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.28</v>
       </c>
-      <c r="H8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U8" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Y8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+        <v>2.49</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
@@ -1466,7 +1490,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4513307</v>
+        <v>4549595</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1475,77 +1499,93 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ROM2</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bihor</t>
+          <t>Ararat-Armenia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csm Resita</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.93</v>
       </c>
-      <c r="H9" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.39</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>2.13</v>
+      </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
@@ -1573,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4571525</v>
+        <v>4549590</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1582,92 +1622,92 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IRAN</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tractor Fc</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Nijmegen</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="I10" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R10" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
@@ -1696,7 +1736,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4522605</v>
+        <v>4549660</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1705,92 +1745,92 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SUUD</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.97</v>
+        <v>8.66</v>
       </c>
       <c r="H11" t="n">
-        <v>2.83</v>
+        <v>5.51</v>
       </c>
       <c r="I11" t="n">
-        <v>2.69</v>
+        <v>1.13</v>
       </c>
       <c r="J11" t="n">
-        <v>1.16</v>
+        <v>3.18</v>
       </c>
       <c r="K11" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.56</v>
+        <v>2.28</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="O11" t="n">
-        <v>2.97</v>
+        <v>4.86</v>
       </c>
       <c r="P11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R11" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.52</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>4.81</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -1819,7 +1859,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4549657</v>
+        <v>4549661</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1828,7 +1868,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1838,82 +1878,82 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4.39</v>
+        <v>1.59</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="I12" t="n">
-        <v>1.47</v>
+        <v>4.15</v>
       </c>
       <c r="J12" t="n">
-        <v>1.92</v>
+        <v>1.07</v>
       </c>
       <c r="K12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.75</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.79</v>
-      </c>
       <c r="Q12" t="n">
-        <v>3.37</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6</v>
+        <v>18.2</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="T12" t="n">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="U12" t="n">
-        <v>1.99</v>
+        <v>4.72</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="X12" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.37</v>
+        <v>2.69</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.43</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.74</v>
+        <v>3.33</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
@@ -1942,7 +1982,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4536735</v>
+        <v>4549593</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1951,88 +1991,92 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAT</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shahaniya</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Marsilya</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5.63</v>
+        <v>3.03</v>
       </c>
       <c r="H13" t="n">
-        <v>4.93</v>
+        <v>3.18</v>
       </c>
       <c r="I13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L13" t="n">
         <v>1.17</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
       <c r="M13" t="n">
-        <v>3.11</v>
+        <v>1.93</v>
       </c>
       <c r="N13" t="n">
-        <v>1.09</v>
+        <v>1.49</v>
       </c>
       <c r="O13" t="n">
-        <v>8.07</v>
+        <v>3.98</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.27</v>
+        <v>3.01</v>
       </c>
       <c r="R13" t="n">
-        <v>3.67</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>5.13</v>
+        <v>3.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.71</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>2.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+        <v>2.19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>1.31</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
@@ -2061,7 +2105,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4522604</v>
+        <v>4549589</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2070,92 +2114,92 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SUUD</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Union St.G</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Shabab (Riya</t>
+          <t>Hapoel Beer She</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.65</v>
       </c>
-      <c r="H14" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.72</v>
-      </c>
       <c r="R14" t="n">
-        <v>7.5</v>
+        <v>6.46</v>
       </c>
       <c r="S14" t="n">
-        <v>3.08</v>
+        <v>1.51</v>
       </c>
       <c r="T14" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.31</v>
+        <v>7</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="X14" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.04</v>
+        <v>5.09</v>
       </c>
       <c r="AA14" t="n">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
@@ -2184,7 +2228,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4537788</v>
+        <v>4549662</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2193,73 +2237,93 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MLTP</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Kauno Zalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Birkirkara</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="H15" t="n">
-        <v>2.96</v>
+        <v>3.42</v>
       </c>
       <c r="I15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.78</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.46</v>
       </c>
       <c r="K15" t="n">
         <v>1.13</v>
       </c>
       <c r="L15" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="M15" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+        <v>1.56</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11.1</v>
+      </c>
       <c r="S15" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.65</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.57</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -2287,7 +2351,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4484982</v>
+        <v>4549659</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2296,77 +2360,93 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KARA</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buducnost</t>
+          <t>Pafos Fc</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fk Arsenal Tiva</t>
+          <t>Riga Fc</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="H16" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="I16" t="n">
-        <v>5.02</v>
+        <v>4.45</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R16" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.08</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.52</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -2394,7 +2474,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4450290</v>
+        <v>4549658</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2403,73 +2483,93 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EST2</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flora Tallinn </t>
+          <t>Kizilyildiz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nomme United Ii</t>
+          <t>Kopenhag</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="H17" t="n">
-        <v>3.76</v>
+        <v>3.21</v>
       </c>
       <c r="I17" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="J17" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="K17" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+        <v>1.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R17" t="n">
+        <v>9.33</v>
+      </c>
       <c r="S17" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="T17" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>2.87</v>
+        <v>3.24</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
+        <v>2.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.35</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -2497,7 +2597,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4549594</v>
+        <v>4575333</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2516,82 +2616,82 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.37</v>
+        <v>4.31</v>
       </c>
       <c r="H18" t="n">
-        <v>3.87</v>
+        <v>3.58</v>
       </c>
       <c r="I18" t="n">
-        <v>5.01</v>
+        <v>1.47</v>
       </c>
       <c r="J18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>12</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.12</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="R18" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.24</v>
-      </c>
       <c r="U18" t="n">
-        <v>5.18</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X18" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.88</v>
+        <v>3.51</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
@@ -2620,7 +2720,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4549550</v>
+        <v>4536738</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2634,87 +2734,83 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>KAT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gharrafa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>3.37</v>
       </c>
       <c r="I19" t="n">
-        <v>7.3</v>
+        <v>2.47</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="L19" t="n">
-        <v>2.86</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>5.22</v>
+        <v>5.28</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
-        <v>6.36</v>
+        <v>5.8</v>
       </c>
       <c r="S19" t="n">
-        <v>1.54</v>
+        <v>2.32</v>
       </c>
       <c r="T19" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>6.57</v>
+        <v>2.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.8</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
@@ -2743,7 +2839,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4549665</v>
+        <v>4549592</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2757,87 +2853,87 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fc Iberia</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2.82</v>
+        <v>1.16</v>
       </c>
       <c r="H20" t="n">
-        <v>3.05</v>
+        <v>4.94</v>
       </c>
       <c r="I20" t="n">
-        <v>1.98</v>
+        <v>7.89</v>
       </c>
       <c r="J20" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="N20" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>4.21</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.52</v>
+        <v>2.91</v>
       </c>
       <c r="R20" t="n">
-        <v>14</v>
+        <v>8.67</v>
       </c>
       <c r="S20" t="n">
-        <v>3.42</v>
+        <v>1.55</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>2.57</v>
+        <v>7.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="W20" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.49</v>
+        <v>2.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>4.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
@@ -2866,7 +2962,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4549595</v>
+        <v>4549591</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2885,82 +2981,82 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ararat-Armenia</t>
+          <t>Ofi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>B.Leverkusen</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5.04</v>
+        <v>9.76</v>
       </c>
       <c r="H21" t="n">
-        <v>4.09</v>
+        <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="J21" t="n">
-        <v>2.19</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>2.15</v>
+        <v>2.78</v>
       </c>
       <c r="N21" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="O21" t="n">
-        <v>4.54</v>
+        <v>6.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>7.73</v>
+        <v>4.94</v>
       </c>
       <c r="S21" t="n">
-        <v>5.08</v>
+        <v>7.88</v>
       </c>
       <c r="T21" t="n">
-        <v>2.35</v>
+        <v>2.89</v>
       </c>
       <c r="U21" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.52</v>
+        <v>6.22</v>
       </c>
       <c r="AA21" t="n">
         <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
@@ -2989,7 +3085,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4549590</v>
+        <v>4549664</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3003,87 +3099,87 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Nordsjaelland</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nijmegen</t>
+          <t>Cska Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.47</v>
       </c>
-      <c r="H22" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Y22" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.53</v>
+        <v>4.63</v>
       </c>
       <c r="AA22" t="n">
         <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
@@ -3112,7 +3208,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4549660</v>
+        <v>4549663</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3131,82 +3227,82 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Inter Escaldes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Universitatea C</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8.66</v>
+        <v>4.82</v>
       </c>
       <c r="H23" t="n">
-        <v>5.51</v>
+        <v>3.59</v>
       </c>
       <c r="I23" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="J23" t="n">
-        <v>3.18</v>
+        <v>2.01</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="O23" t="n">
-        <v>4.86</v>
+        <v>3.21</v>
       </c>
       <c r="P23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="S23" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.48</v>
-      </c>
       <c r="V23" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X23" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.81</v>
+        <v>3.27</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
@@ -3235,7 +3331,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4549661</v>
+        <v>4522603</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3244,92 +3340,88 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>SUUD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Al Ahli (Cidde</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.59</v>
+        <v>1.15</v>
       </c>
       <c r="H24" t="n">
-        <v>3.17</v>
+        <v>4.74</v>
       </c>
       <c r="I24" t="n">
-        <v>4.15</v>
+        <v>6.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.76</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="O24" t="n">
-        <v>2.82</v>
+        <v>4.85</v>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>18.2</v>
+        <v>6.48</v>
       </c>
       <c r="S24" t="n">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="U24" t="n">
-        <v>4.72</v>
+        <v>6.21</v>
       </c>
       <c r="V24" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="W24" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.19</v>
-      </c>
+        <v>1.82</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
@@ -3358,7 +3450,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4549593</v>
+        <v>4537791</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3367,93 +3459,77 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>MLTP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hibernians</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marsilya</t>
+          <t>Gzira United</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3.03</v>
+        <v>1.63</v>
       </c>
       <c r="H25" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="I25" t="n">
-        <v>1.85</v>
+        <v>3.29</v>
       </c>
       <c r="J25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.54</v>
       </c>
-      <c r="K25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R25" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W25" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="X25" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.37</v>
-      </c>
+        <v>2.34</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
@@ -3481,7 +3557,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4549589</v>
+        <v>4549598</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3490,7 +3566,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3500,82 +3576,82 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Union St.G</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Beer She</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.15</v>
+        <v>5.2</v>
       </c>
       <c r="H26" t="n">
-        <v>5.25</v>
+        <v>4.11</v>
       </c>
       <c r="I26" t="n">
-        <v>7.95</v>
+        <v>1.33</v>
       </c>
       <c r="J26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3</v>
-      </c>
       <c r="M26" t="n">
-        <v>2.37</v>
+        <v>2.04</v>
       </c>
       <c r="N26" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="O26" t="n">
-        <v>5.16</v>
+        <v>4.19</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="R26" t="n">
-        <v>6.46</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>1.51</v>
+        <v>5.27</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>1.77</v>
       </c>
       <c r="V26" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="X26" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.09</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
@@ -3604,7 +3680,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4549662</v>
+        <v>4549666</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3613,7 +3689,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3623,82 +3699,82 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kauno Zalgiris</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3.83</v>
+        <v>1.93</v>
       </c>
       <c r="H27" t="n">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="I27" t="n">
-        <v>1.58</v>
+        <v>2.73</v>
       </c>
       <c r="J27" t="n">
-        <v>1.78</v>
+        <v>1.21</v>
       </c>
       <c r="K27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="L27" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="M27" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="N27" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.62</v>
+        <v>4.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U27" t="n">
         <v>3.2</v>
       </c>
-      <c r="R27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W27" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="X27" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
@@ -3727,7 +3803,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4549659</v>
+        <v>4549667</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3736,7 +3812,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3746,82 +3822,82 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pafos Fc</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Riga Fc</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="H28" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="I28" t="n">
-        <v>4.45</v>
+        <v>4.37</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="R28" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.11</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R28" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AC28" t="n">
-        <v>2.52</v>
+        <v>3.46</v>
       </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
@@ -3850,7 +3926,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4549658</v>
+        <v>4549670</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3859,7 +3935,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3869,82 +3945,82 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kizilyildiz</t>
+          <t>Borac Banja Lu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kopenhag</t>
+          <t>Kuopion</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="H29" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="I29" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="K29" t="n">
         <v>1.15</v>
       </c>
       <c r="L29" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="M29" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="N29" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>4.02</v>
+        <v>3.11</v>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="R29" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.99</v>
-      </c>
-      <c r="R29" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.35</v>
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
@@ -3973,7 +4049,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4575333</v>
+        <v>4549671</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3982,92 +4058,92 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Lincoln Red Im</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4.31</v>
+        <v>10.4</v>
       </c>
       <c r="H30" t="n">
-        <v>3.58</v>
+        <v>6.12</v>
       </c>
       <c r="I30" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="J30" t="n">
-        <v>1.92</v>
+        <v>3.61</v>
       </c>
       <c r="K30" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1.79</v>
+        <v>2.44</v>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="O30" t="n">
-        <v>3.47</v>
+        <v>5.35</v>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>6.18</v>
       </c>
       <c r="S30" t="n">
-        <v>4.72</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.77</v>
       </c>
       <c r="U30" t="n">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="V30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.61</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.76</v>
-      </c>
       <c r="X30" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.51</v>
+        <v>5.27</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
@@ -4096,7 +4172,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4536738</v>
+        <v>4549597</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4105,88 +4181,92 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KAT</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gharrafa</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="H31" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="I31" t="n">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="J31" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="K31" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="M31" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>5.28</v>
+        <v>4.95</v>
       </c>
       <c r="P31" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="R31" t="n">
-        <v>5.8</v>
+        <v>6.83</v>
       </c>
       <c r="S31" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>2.87</v>
+        <v>3.32</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="W31" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="X31" t="n">
         <v>1.47</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
+        <v>1.96</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
       <c r="AB31" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
@@ -4215,7 +4295,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4549592</v>
+        <v>4549599</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4224,7 +4304,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4234,82 +4314,82 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Viktoria Plzen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Levski Sofya</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="H32" t="n">
-        <v>4.94</v>
+        <v>3.41</v>
       </c>
       <c r="I32" t="n">
-        <v>7.89</v>
+        <v>3.82</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="L32" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="M32" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="N32" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="O32" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R32" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U32" t="n">
         <v>4.21</v>
       </c>
-      <c r="P32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="R32" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U32" t="n">
-        <v>7.22</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="W32" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="X32" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.22</v>
+        <v>3.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
@@ -4338,7 +4418,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4549591</v>
+        <v>4549668</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4347,92 +4427,92 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ofi</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>B.Leverkusen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9.76</v>
+        <v>1.97</v>
       </c>
       <c r="H33" t="n">
-        <v>6.2</v>
+        <v>3.23</v>
       </c>
       <c r="I33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA33" t="n">
         <v>1.08</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="O33" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="S33" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.71</v>
+        <v>2.49</v>
       </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
@@ -4461,7 +4541,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4549664</v>
+        <v>4549604</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4470,92 +4550,92 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nordsjaelland</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cska Sofia</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.22</v>
+        <v>2.36</v>
       </c>
       <c r="H34" t="n">
-        <v>4.61</v>
+        <v>3.07</v>
       </c>
       <c r="I34" t="n">
-        <v>6.56</v>
+        <v>2.28</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="L34" t="n">
-        <v>2.59</v>
+        <v>1.3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="N34" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="O34" t="n">
-        <v>4.66</v>
+        <v>3.5</v>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.77</v>
+        <v>3.27</v>
       </c>
       <c r="R34" t="n">
-        <v>7.44</v>
+        <v>11.75</v>
       </c>
       <c r="S34" t="n">
-        <v>1.61</v>
+        <v>2.92</v>
       </c>
       <c r="T34" t="n">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="U34" t="n">
-        <v>6.15</v>
+        <v>2.85</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="X34" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.63</v>
+        <v>3.56</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
@@ -4584,7 +4664,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4549663</v>
+        <v>4549543</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4593,92 +4673,92 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Escaldes</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitatea C</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4.82</v>
+        <v>1.89</v>
       </c>
       <c r="H35" t="n">
-        <v>3.59</v>
+        <v>3.31</v>
       </c>
       <c r="I35" t="n">
-        <v>1.42</v>
+        <v>2.79</v>
       </c>
       <c r="J35" t="n">
-        <v>2.01</v>
+        <v>1.21</v>
       </c>
       <c r="K35" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="L35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AA35" t="n">
         <v>1</v>
       </c>
-      <c r="M35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
@@ -4707,7 +4787,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4522603</v>
+        <v>4549672</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4716,88 +4796,92 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SUUD</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli (Cidde</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K36" t="n">
         <v>1.15</v>
       </c>
-      <c r="H36" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="I36" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R36" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AA36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U36" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
@@ -4826,7 +4910,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4537791</v>
+        <v>4549605</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4835,77 +4919,93 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MLTP</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hibernians</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gzira United</t>
+          <t>Sparta Prag</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="H37" t="n">
-        <v>3.15</v>
+        <v>3.94</v>
       </c>
       <c r="I37" t="n">
-        <v>3.29</v>
+        <v>5.46</v>
       </c>
       <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
         <v>1.08</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AA37" t="n">
         <v>1.1</v>
       </c>
-      <c r="L37" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X37" t="n">
+      <c r="AB37" t="n">
         <v>1.24</v>
       </c>
-      <c r="Y37" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>2.61</v>
+      </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
@@ -4933,7 +5033,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4549598</v>
+        <v>4549673</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4947,87 +5047,87 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>AVKL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Aarhus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Egnatia</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5.2</v>
+        <v>1.35</v>
       </c>
       <c r="H38" t="n">
-        <v>4.11</v>
+        <v>3.91</v>
       </c>
       <c r="I38" t="n">
-        <v>1.33</v>
+        <v>5.15</v>
       </c>
       <c r="J38" t="n">
-        <v>2.23</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="M38" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="N38" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="O38" t="n">
-        <v>4.19</v>
+        <v>3.7</v>
       </c>
       <c r="P38" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>8.720000000000001</v>
+        <v>10.65</v>
       </c>
       <c r="S38" t="n">
-        <v>5.27</v>
+        <v>1.82</v>
       </c>
       <c r="T38" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="U38" t="n">
-        <v>1.77</v>
+        <v>5.34</v>
       </c>
       <c r="V38" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W38" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="X38" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
@@ -5056,7 +5156,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4549666</v>
+        <v>4549601</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5070,36 +5170,36 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.93</v>
+        <v>4.48</v>
       </c>
       <c r="H39" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="I39" t="n">
-        <v>2.73</v>
+        <v>1.43</v>
       </c>
       <c r="J39" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
         <v>2.06</v>
@@ -5108,49 +5208,49 @@
         <v>1.42</v>
       </c>
       <c r="O39" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="P39" t="n">
         <v>1.87</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="R39" t="n">
-        <v>8.26</v>
+        <v>8.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.43</v>
+        <v>4.68</v>
       </c>
       <c r="T39" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="U39" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W39" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="X39" t="n">
         <v>1.41</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
@@ -5179,7 +5279,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4549667</v>
+        <v>4549669</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5198,19 +5298,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>St. Truidense</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="H40" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="I40" t="n">
         <v>4.37</v>
@@ -5219,61 +5319,61 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="L40" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>1.53</v>
+        <v>2.13</v>
       </c>
       <c r="N40" t="n">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="O40" t="n">
-        <v>2.73</v>
+        <v>4.48</v>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.08</v>
+        <v>2.82</v>
       </c>
       <c r="R40" t="n">
-        <v>19.55</v>
+        <v>7.89</v>
       </c>
       <c r="S40" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="T40" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="U40" t="n">
-        <v>5.02</v>
+        <v>4.58</v>
       </c>
       <c r="V40" t="n">
-        <v>1.84</v>
+        <v>1.46</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.74</v>
+        <v>2.03</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.79</v>
+        <v>4.46</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
@@ -5302,7 +5402,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4549670</v>
+        <v>4549603</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5316,87 +5416,87 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borac Banja Lu</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kuopion</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.71</v>
+        <v>6.79</v>
       </c>
       <c r="H41" t="n">
-        <v>3.17</v>
+        <v>4.64</v>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1.21</v>
       </c>
       <c r="J41" t="n">
-        <v>1.11</v>
+        <v>2.64</v>
       </c>
       <c r="K41" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.64</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="N41" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="O41" t="n">
-        <v>3.11</v>
+        <v>4.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.61</v>
+        <v>2.85</v>
       </c>
       <c r="R41" t="n">
-        <v>14.9</v>
+        <v>8.08</v>
       </c>
       <c r="S41" t="n">
-        <v>2.27</v>
+        <v>6.38</v>
       </c>
       <c r="T41" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="U41" t="n">
-        <v>4.08</v>
+        <v>1.61</v>
       </c>
       <c r="V41" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="W41" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="X41" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.53</v>
+        <v>2.02</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.16</v>
+        <v>4.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.99</v>
+        <v>2.18</v>
       </c>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
@@ -5425,7 +5525,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4549671</v>
+        <v>4549602</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5439,87 +5539,87 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lincoln Red Im</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ac Milan</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>10.4</v>
+        <v>1.87</v>
       </c>
       <c r="H42" t="n">
-        <v>6.12</v>
+        <v>3.23</v>
       </c>
       <c r="I42" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R42" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AA42" t="n">
         <v>1.08</v>
       </c>
-      <c r="J42" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O42" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="S42" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
@@ -5548,7 +5648,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4549597</v>
+        <v>4549600</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5567,82 +5667,82 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Jagiellonia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Anderlecht</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="H43" t="n">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="I43" t="n">
-        <v>2.91</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="K43" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="M43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R43" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y43" t="n">
         <v>2.27</v>
       </c>
-      <c r="N43" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O43" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.96</v>
-      </c>
       <c r="Z43" t="n">
-        <v>4.9</v>
+        <v>3.76</v>
       </c>
       <c r="AA43" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
@@ -5671,101 +5771,101 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4549599</v>
+        <v>4573617</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>LKU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Viktoria Plzen</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Levski Sofya</t>
+          <t>Estudiantes Lp</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="H44" t="n">
-        <v>3.41</v>
+        <v>4.19</v>
       </c>
       <c r="I44" t="n">
-        <v>3.82</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="L44" t="n">
-        <v>1.77</v>
+        <v>2.65</v>
       </c>
       <c r="M44" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="N44" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
-        <v>3.83</v>
+        <v>2.78</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.09</v>
+        <v>4.01</v>
       </c>
       <c r="R44" t="n">
-        <v>10.1</v>
+        <v>18.9</v>
       </c>
       <c r="S44" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="T44" t="n">
         <v>2.14</v>
       </c>
       <c r="U44" t="n">
-        <v>4.21</v>
+        <v>8.09</v>
       </c>
       <c r="V44" t="n">
-        <v>1.49</v>
+        <v>2.26</v>
       </c>
       <c r="W44" t="n">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="X44" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.22</v>
+        <v>2.65</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.85</v>
+        <v>2.84</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.45</v>
+        <v>3.39</v>
       </c>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
@@ -5794,102 +5894,86 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4549668</v>
+        <v>4503505</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AVKL</t>
+          <t>MEK2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Alebrijes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Cruz Azul Hidal</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="H45" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="J45" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="L45" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M45" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R45" t="n">
-        <v>10.45</v>
-      </c>
+        <v>1.44</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="T45" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="U45" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V45" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="X45" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.49</v>
-      </c>
+        <v>2.08</v>
+      </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
@@ -5917,102 +6001,86 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4549604</v>
+        <v>4513954</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>KOL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Atletico Nacio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="H46" t="n">
-        <v>3.07</v>
+        <v>4.73</v>
       </c>
       <c r="I46" t="n">
-        <v>2.28</v>
+        <v>8.48</v>
       </c>
       <c r="J46" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.3</v>
+        <v>2.71</v>
       </c>
       <c r="M46" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="N46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="R46" t="n">
-        <v>11.75</v>
-      </c>
+        <v>1.41</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>2.92</v>
+        <v>1.46</v>
       </c>
       <c r="T46" t="n">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="U46" t="n">
-        <v>2.85</v>
+        <v>7.67</v>
       </c>
       <c r="V46" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="W46" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="X46" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.65</v>
-      </c>
+        <v>1.99</v>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
@@ -6040,101 +6108,89 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4549543</v>
+        <v>4538567</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>SİNP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Lion City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W47" t="n">
         <v>1.89</v>
       </c>
-      <c r="H47" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O47" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W47" t="n">
-        <v>2.26</v>
-      </c>
       <c r="X47" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1</v>
-      </c>
+        <v>2.02</v>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
@@ -6161,1438 +6217,6 @@
       <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="inlineStr"/>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>4549672</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>AVKL</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Thun</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Hajduk Split</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O48" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="R48" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W48" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
-      <c r="AR48" t="inlineStr"/>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AU48" t="inlineStr"/>
-      <c r="AV48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr"/>
-      <c r="BA48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>4549605</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>AVL</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Olympiakos</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Sparta Prag</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="H49" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="I49" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="R49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U49" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr"/>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AU49" t="inlineStr"/>
-      <c r="AV49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr"/>
-      <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
-      <c r="BA49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>4549673</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>AVKL</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Aarhus</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Egnatia</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="I50" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R50" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U50" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr"/>
-      <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr"/>
-      <c r="BA50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>4549601</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>AVL</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Celje</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Salzburg</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="R51" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="S51" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
-      <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr"/>
-      <c r="BA51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>4549669</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>AVKL</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Midtjylland</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>St. Truidense</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H52" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I52" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O52" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U52" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W52" t="n">
-        <v>2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="inlineStr"/>
-      <c r="AQ52" t="inlineStr"/>
-      <c r="AR52" t="inlineStr"/>
-      <c r="AS52" t="inlineStr"/>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AU52" t="inlineStr"/>
-      <c r="AV52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr"/>
-      <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr"/>
-      <c r="BA52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>4549603</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>AVL</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Omonia</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Benfica</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="H53" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R53" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="S53" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr"/>
-      <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>4549602</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>AVL</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Bournemouth</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Ac Milan</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H54" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O54" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R54" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W54" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
-      <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr"/>
-      <c r="AS54" t="inlineStr"/>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="inlineStr"/>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
-      <c r="BA54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>4549600</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>22.10.2026</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>AVL</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Jagiellonia</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Anderlecht</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O55" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R55" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U55" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W55" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
-      <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="inlineStr"/>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="inlineStr"/>
-      <c r="AV55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr"/>
-      <c r="AX55" t="inlineStr"/>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr"/>
-      <c r="BA55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>4573617</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>23.10.2026</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LKU</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Estudiantes Lp</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H56" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="R56" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U56" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="V56" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
-      <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="inlineStr"/>
-      <c r="AV56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr"/>
-      <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>4503505</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>23.10.2026</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>MEK2</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Alebrijes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Cruz Azul Hidal</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H57" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U57" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="inlineStr"/>
-      <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="inlineStr"/>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AU57" t="inlineStr"/>
-      <c r="AV57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr"/>
-      <c r="AX57" t="inlineStr"/>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr"/>
-      <c r="BA57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>4513954</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>23.10.2026</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>KOL</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Atletico Nacio</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Deportivo Pasto</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U58" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X58" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
-      <c r="AQ58" t="inlineStr"/>
-      <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="inlineStr"/>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AU58" t="inlineStr"/>
-      <c r="AV58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr"/>
-      <c r="AX58" t="inlineStr"/>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr"/>
-      <c r="BA58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>4538567</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>25.10.2026</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SİNP</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Lion City</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tanjong Pagar</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H59" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T59" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U59" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X59" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
-      <c r="AR59" t="inlineStr"/>
-      <c r="AS59" t="inlineStr"/>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr"/>
-      <c r="AV59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr"/>
-      <c r="AX59" t="inlineStr"/>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr"/>
-      <c r="BA59" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/oranlar_yaklasan.xlsx
+++ b/oranlar_yaklasan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA66"/>
+  <dimension ref="A1:BA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,7 +685,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4476473</v>
+        <v>4476476</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -704,82 +704,82 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Club Tijuana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="I2" t="n">
-        <v>3.91</v>
+        <v>3.02</v>
       </c>
       <c r="J2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -808,7 +808,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4501896</v>
+        <v>4550378</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -817,32 +817,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>ENDL1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Deportivo Garc</t>
+          <t>Bhayangkara Su</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chankas Cyc</t>
+          <t>Psm Makassar</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>5.12</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -851,38 +851,38 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="M3" t="n">
         <v>1.89</v>
       </c>
       <c r="N3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>5.39</v>
+        <v>5.21</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X3" t="n">
         <v>1.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4435995</v>
+        <v>4550379</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ŞİL</t>
+          <t>ENDL1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Univ De Concep</t>
+          <t>Persija Jakart</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportes Limach</t>
+          <t>Persik</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>1.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.11</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2.07</v>
+        <v>7.98</v>
       </c>
       <c r="J4" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.41</v>
-      </c>
+        <v>2.84</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>2.81</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="U4" t="n">
-        <v>2.57</v>
+        <v>6.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.64</v>
+      </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4513979</v>
+        <v>4550377</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1031,72 +1031,72 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KOL</t>
+          <t>ENDL1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atletico Nacio</t>
+          <t>Persebaya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Independiente M</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="H5" t="n">
-        <v>3.37</v>
+        <v>3.83</v>
       </c>
       <c r="I5" t="n">
-        <v>4.21</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="N5" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>4.49</v>
+        <v>5.43</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4576811</v>
+        <v>4550142</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1138,77 +1138,93 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>AŞMP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo La G</t>
+          <t>Neftchi Fargon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metropolitanos </t>
+          <t>Al Ittihad (Cid</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>2.06</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.58</v>
-      </c>
       <c r="N6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.32</v>
+      </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>4.26</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="U6" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+        <v>1.92</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.01</v>
+      </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1236,7 +1252,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4490433</v>
+        <v>4572335</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1245,77 +1261,93 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GUAT</t>
+          <t>HİNSL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suchitepequez</t>
+          <t>Atk Mohun Baga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Chennaiyin Fc</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="H7" t="n">
-        <v>3.07</v>
+        <v>4.68</v>
       </c>
       <c r="I7" t="n">
-        <v>3.73</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+        <v>1.47</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R7" t="n">
+        <v>10.15</v>
+      </c>
       <c r="S7" t="n">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>4.2</v>
+        <v>7.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="W7" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+        <v>2.08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.36</v>
+      </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1343,7 +1375,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4487099</v>
+        <v>4513304</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1352,77 +1384,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KOSTA</t>
+          <t>ROM2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alajuelense</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Perez Zeledon</t>
+          <t>Ramnicu Valcea</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.12</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
-        <v>4.83</v>
+        <v>2.84</v>
       </c>
       <c r="I8" t="n">
-        <v>7.63</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
-        <v>6.93</v>
+        <v>3.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
@@ -1450,7 +1482,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4560785</v>
+        <v>4476037</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1459,73 +1491,69 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MEKKA</t>
+          <t>BUL1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tigres Uanl (K</t>
+          <t>Lokomotiv Plov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monterrey (K)</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="H9" t="n">
-        <v>3.18</v>
+        <v>2.72</v>
       </c>
       <c r="I9" t="n">
-        <v>2.72</v>
+        <v>3.07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>3.18</v>
+        <v>3.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="W9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.01</v>
-      </c>
+        <v>1.44</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
@@ -1557,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4475904</v>
+        <v>4435457</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1566,93 +1594,59 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ARJ</t>
+          <t>GUR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Corboda Santia</t>
+          <t>Fc Iberia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.79</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="I10" t="n">
-        <v>2.11</v>
+        <v>3.16</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="L10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="R10" t="n">
-        <v>23</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.75</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -1680,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4475914</v>
+        <v>4505880</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1689,93 +1683,77 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ARJ</t>
+          <t>BULB</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barracas</t>
+          <t>Ludogorets Ii</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rio Cuarto</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="H11" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="I11" t="n">
-        <v>6.12</v>
+        <v>4.29</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="R11" t="n">
-        <v>34.5</v>
-      </c>
+        <v>1.66</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>7.02</v>
+        <v>4.75</v>
       </c>
       <c r="V11" t="n">
-        <v>2.53</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.26</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.27</v>
-      </c>
+        <v>2.38</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -1803,7 +1781,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4419811</v>
+        <v>4542732</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1812,92 +1790,92 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ABD</t>
+          <t>TSL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Los Angeles Fc</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Başakşehir Fk</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="H12" t="n">
-        <v>4.21</v>
+        <v>4.96</v>
       </c>
       <c r="I12" t="n">
-        <v>4.68</v>
+        <v>6.32</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="M12" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="O12" t="n">
-        <v>5.74</v>
+        <v>6.03</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>5.65</v>
+        <v>5.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="U12" t="n">
-        <v>4.66</v>
+        <v>5.79</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.61</v>
+        <v>5.86</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
@@ -1926,7 +1904,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4476475</v>
+        <v>4484901</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1935,93 +1913,59 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MEK</t>
+          <t>LIT1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Transinvest Vi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Fa Siauliai Ii</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3.11</v>
+        <v>1.93</v>
       </c>
       <c r="H13" t="n">
-        <v>3.18</v>
+        <v>3.43</v>
       </c>
       <c r="I13" t="n">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="J13" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="L13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R13" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.19</v>
-      </c>
+        <v>1.38</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
@@ -2049,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4476474</v>
+        <v>4441284</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2058,93 +2002,73 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MEK</t>
+          <t>ARJPBN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>San Martin Sj</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="H14" t="n">
-        <v>3.66</v>
+        <v>2.46</v>
       </c>
       <c r="I14" t="n">
-        <v>4.43</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="L14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7.65</v>
-      </c>
+        <v>1.23</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>1.77</v>
+        <v>3.22</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>4.57</v>
+        <v>3.32</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.99</v>
       </c>
       <c r="W14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
         <v>1.94</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.99</v>
-      </c>
       <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.06</v>
-      </c>
+        <v>1.39</v>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -2172,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4513980</v>
+        <v>4446800</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2181,77 +2105,77 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KOL</t>
+          <t>LET</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportes Tolim</t>
+          <t>Grobina</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Riga Fc</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.28</v>
+        <v>9.24</v>
       </c>
       <c r="H15" t="n">
-        <v>3.61</v>
+        <v>5.46</v>
       </c>
       <c r="I15" t="n">
-        <v>5.81</v>
+        <v>1.06</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2.98</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.73</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>1.74</v>
+        <v>7.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.01</v>
+        <v>2.67</v>
       </c>
       <c r="U15" t="n">
-        <v>6.12</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.76</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -2279,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4476476</v>
+        <v>4542728</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2288,92 +2212,92 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MEK</t>
+          <t>TSL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Tijuana</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>3.02</v>
+        <v>1.74</v>
       </c>
       <c r="J16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K16" t="n">
         <v>1.12</v>
       </c>
-      <c r="K16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="M16" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="N16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4.05</v>
+        <v>4.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="R16" t="n">
-        <v>8.41</v>
+        <v>7.79</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>3.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3.43</v>
+        <v>2.22</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.79</v>
+        <v>4.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
@@ -2402,7 +2326,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4550378</v>
+        <v>4498094</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2411,73 +2335,69 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ENDL1</t>
+          <t>RUS1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bhayangkara Su</t>
+          <t>Shinnik Yarosl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Psm Makassar</t>
+          <t>Spartak Kostrom</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.28</v>
+        <v>2.21</v>
       </c>
       <c r="H17" t="n">
-        <v>3.87</v>
+        <v>2.68</v>
       </c>
       <c r="I17" t="n">
-        <v>5.12</v>
+        <v>2.45</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="L17" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.7</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U17" t="n">
-        <v>5.21</v>
+        <v>3.23</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.03</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
@@ -2509,7 +2429,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4550379</v>
+        <v>4477533</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2518,77 +2438,77 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ENDL1</t>
+          <t>LITA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Persija Jakart</t>
+          <t>Kauno Zalgiris</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Persik</t>
+          <t>Zalgiris Vilniu</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>3.36</v>
       </c>
       <c r="I18" t="n">
-        <v>7.98</v>
+        <v>3.72</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="L18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.48</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="T18" t="n">
-        <v>2.71</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>6.83</v>
+        <v>4.13</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="X18" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.64</v>
-      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
@@ -2616,7 +2536,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4550377</v>
+        <v>4498857</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2625,72 +2545,72 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ENDL1</t>
+          <t>T1L</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Persebaya</t>
+          <t>Mardin 1969</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Manisa Futbol K</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="H19" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>3.69</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>5.43</v>
+        <v>4.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -2723,7 +2643,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4550142</v>
+        <v>4486231</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2732,92 +2652,92 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AŞMP</t>
+          <t>POL1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftchi Fargon</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad (Cid</t>
+          <t>Lks Lodz</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
-        <v>3.73</v>
+        <v>2.98</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="J20" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="N20" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="O20" t="n">
-        <v>4.44</v>
+        <v>3.58</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.71</v>
+        <v>3.05</v>
       </c>
       <c r="R20" t="n">
-        <v>7.32</v>
+        <v>10.3</v>
       </c>
       <c r="S20" t="n">
-        <v>4.26</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.83</v>
+        <v>2.58</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
         <v>1.94</v>
       </c>
       <c r="X20" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.09</v>
+        <v>3.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
@@ -2846,7 +2766,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4572335</v>
+        <v>4474311</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2855,92 +2775,92 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HİNSL</t>
+          <t>HIR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atk Mohun Baga</t>
+          <t>Istra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chennaiyin Fc</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.11</v>
+        <v>3.53</v>
       </c>
       <c r="H21" t="n">
-        <v>4.68</v>
+        <v>3.29</v>
       </c>
       <c r="I21" t="n">
-        <v>8.609999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="J21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R21" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R21" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U21" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
@@ -2969,7 +2889,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4513304</v>
+        <v>4450302</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2978,73 +2898,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ROM2</t>
+          <t>EST2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Viimsi Mrjk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ramnicu Valcea</t>
+          <t>Flora Tallinn I</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="H22" t="n">
-        <v>2.84</v>
+        <v>3.79</v>
       </c>
       <c r="I22" t="n">
-        <v>2.88</v>
+        <v>3.59</v>
       </c>
       <c r="J22" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K22" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.66</v>
-      </c>
+        <v>1.76</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.39</v>
-      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
@@ -3076,7 +2978,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4476037</v>
+        <v>4537797</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3085,69 +2987,73 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BUL1</t>
+          <t>MLTP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plov</t>
+          <t>Zabbar St Patr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.86</v>
+        <v>4.27</v>
       </c>
       <c r="H23" t="n">
-        <v>2.72</v>
+        <v>3.52</v>
       </c>
       <c r="I23" t="n">
-        <v>3.07</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="K23" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>4.64</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="U23" t="n">
-        <v>3.91</v>
+        <v>1.87</v>
       </c>
       <c r="V23" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="W23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+        <v>1.68</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.19</v>
+      </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
@@ -3179,7 +3085,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4435457</v>
+        <v>4476034</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3188,55 +3094,73 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GUR</t>
+          <t>BUL1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fc Iberia</t>
+          <t>Cska Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="H24" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="I24" t="n">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="K24" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
@@ -3268,7 +3192,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4505880</v>
+        <v>4474505</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3277,77 +3201,93 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BULB</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ludogorets Ii</t>
+          <t>Kopenhag</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Odense</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="H25" t="n">
-        <v>3.28</v>
+        <v>4.66</v>
       </c>
       <c r="I25" t="n">
-        <v>4.29</v>
+        <v>6.48</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>1.59</v>
+        <v>2.25</v>
       </c>
       <c r="N25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7.11</v>
+      </c>
       <c r="S25" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="T25" t="n">
-        <v>1.98</v>
+        <v>2.49</v>
       </c>
       <c r="U25" t="n">
-        <v>4.75</v>
+        <v>6.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="X25" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
+        <v>1.94</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
@@ -3375,7 +3315,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4542732</v>
+        <v>4501635</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3384,92 +3324,92 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TSL</t>
+          <t>ROM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Başakşehir Fk</t>
+          <t>Universitatea C</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.21</v>
+        <v>4.82</v>
       </c>
       <c r="H26" t="n">
-        <v>4.96</v>
+        <v>3.53</v>
       </c>
       <c r="I26" t="n">
-        <v>6.32</v>
+        <v>1.34</v>
       </c>
       <c r="J26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.66</v>
-      </c>
       <c r="M26" t="n">
-        <v>2.65</v>
+        <v>1.64</v>
       </c>
       <c r="N26" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>6.03</v>
+        <v>3.11</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>3.39</v>
       </c>
       <c r="R26" t="n">
-        <v>5.33</v>
+        <v>13.3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.57</v>
+        <v>5.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.64</v>
+        <v>2.04</v>
       </c>
       <c r="U26" t="n">
-        <v>5.79</v>
+        <v>1.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W26" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="X26" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.86</v>
+        <v>3.03</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.77</v>
+        <v>2.69</v>
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
@@ -3498,7 +3438,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4484901</v>
+        <v>4419081</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3507,53 +3447,67 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LIT1</t>
+          <t>ARJPBM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Transinvest Vi</t>
+          <t>Urquiza</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fa Siauliai Ii</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.93</v>
+        <v>1.32</v>
       </c>
       <c r="H27" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="I27" t="n">
-        <v>2.37</v>
+        <v>5.86</v>
       </c>
       <c r="J27" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>1.08</v>
       </c>
       <c r="L27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>1.98</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.88</v>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.36</v>
+      </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
@@ -3587,7 +3541,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4441284</v>
+        <v>4427051</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3596,73 +3550,93 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ARJPBN</t>
+          <t>İSÇ2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Martin Sj</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="H28" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="I28" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="J28" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="K28" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="L28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R28" t="n">
+        <v>10.45</v>
+      </c>
       <c r="S28" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>3.32</v>
+        <v>2.79</v>
       </c>
       <c r="V28" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
+        <v>1.93</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.18</v>
+      </c>
       <c r="Z28" t="n">
-        <v>1.94</v>
+        <v>3.39</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
+        <v>1.07</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.39</v>
+      </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
@@ -3690,7 +3664,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4446800</v>
+        <v>4550147</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3699,62 +3673,74 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LET</t>
+          <t>AŞMP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grobina</t>
+          <t>Al Nassr (Riya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Riga Fc</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9.24</v>
+        <v>1.14</v>
       </c>
       <c r="H29" t="n">
-        <v>5.46</v>
+        <v>4.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.06</v>
+        <v>7.01</v>
       </c>
       <c r="J29" t="n">
-        <v>2.98</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+        <v>2.54</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5.47</v>
+      </c>
       <c r="S29" t="n">
-        <v>7.77</v>
+        <v>1.47</v>
       </c>
       <c r="T29" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>6.24</v>
       </c>
       <c r="V29" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="X29" t="n">
         <v>1.53</v>
@@ -3762,13 +3748,17 @@
       <c r="Y29" t="n">
         <v>1.73</v>
       </c>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
@@ -3797,7 +3787,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4542728</v>
+        <v>4441272</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3806,93 +3796,73 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TSL</t>
+          <t>ARJPBN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>D Belgrano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="H30" t="n">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="I30" t="n">
-        <v>1.74</v>
+        <v>3.71</v>
       </c>
       <c r="J30" t="n">
-        <v>1.61</v>
+        <v>1.06</v>
       </c>
       <c r="K30" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="L30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="P30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.14</v>
-      </c>
+        <v>1.41</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
@@ -3920,7 +3890,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4498094</v>
+        <v>4542731</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3929,73 +3899,93 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RUS1</t>
+          <t>TSL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shinnik Yarosl</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Kostrom</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>2.68</v>
+        <v>3.38</v>
       </c>
       <c r="I31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O31" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W31" t="n">
         <v>2.45</v>
       </c>
-      <c r="J31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.48</v>
       </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>1.95</v>
+      </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
@@ -4023,7 +4013,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4477533</v>
+        <v>4517033</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4032,77 +4022,93 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LITA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kauno Zalgiris</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zalgiris Vilniu</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.8</v>
       </c>
       <c r="X32" t="n">
         <v>1.31</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
+        <v>2.35</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.78</v>
+      </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
@@ -4130,7 +4136,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4498857</v>
+        <v>4535920</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4139,77 +4145,93 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T1L</t>
+          <t>İTC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mardin 1969</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Manisa Futbol K</t>
+          <t>Casarano</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="H33" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="I33" t="n">
-        <v>3.69</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="K33" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="L33" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="N33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+        <v>1.54</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R33" t="n">
+        <v>11.3</v>
+      </c>
       <c r="S33" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="T33" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U33" t="n">
-        <v>4.16</v>
+        <v>3.45</v>
       </c>
       <c r="V33" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="X33" t="n">
         <v>1.28</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
+        <v>2.22</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.48</v>
+      </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
@@ -4237,7 +4259,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4486231</v>
+        <v>4535924</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4246,92 +4268,92 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>POL1</t>
+          <t>İTC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lks Lodz</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="H34" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="I34" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="J34" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="K34" t="n">
         <v>1.13</v>
       </c>
       <c r="L34" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="M34" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="N34" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="O34" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="P34" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="R34" t="n">
-        <v>10.3</v>
+        <v>12.75</v>
       </c>
       <c r="S34" t="n">
-        <v>2.92</v>
+        <v>3.37</v>
       </c>
       <c r="T34" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="U34" t="n">
-        <v>2.58</v>
+        <v>2.39</v>
       </c>
       <c r="V34" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W34" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="X34" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
@@ -4360,7 +4382,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4474311</v>
+        <v>4492791</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4369,92 +4391,92 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HIR</t>
+          <t>İS2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Istra</t>
+          <t>Fc Andorra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3.53</v>
+        <v>1.71</v>
       </c>
       <c r="H35" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="I35" t="n">
-        <v>1.54</v>
+        <v>3.55</v>
       </c>
       <c r="J35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L35" t="n">
         <v>1.64</v>
       </c>
-      <c r="K35" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.07</v>
-      </c>
       <c r="M35" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="N35" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="O35" t="n">
-        <v>3.87</v>
+        <v>3.02</v>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="R35" t="n">
-        <v>9.02</v>
+        <v>15.7</v>
       </c>
       <c r="S35" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="T35" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>4.14</v>
       </c>
       <c r="V35" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="W35" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="X35" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.23</v>
+        <v>3.07</v>
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
@@ -4483,7 +4505,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4450302</v>
+        <v>4537798</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4492,55 +4514,73 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EST2</t>
+          <t>MLTP</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Viimsi Mrjk</t>
+          <t>Mosta Fc</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Flora Tallinn I</t>
+          <t>Hibernians</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1.45</v>
+        <v>2.92</v>
       </c>
       <c r="H36" t="n">
-        <v>3.79</v>
+        <v>3.17</v>
       </c>
       <c r="I36" t="n">
-        <v>3.59</v>
+        <v>1.74</v>
       </c>
       <c r="J36" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+        <v>1.13</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.58</v>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.31</v>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
@@ -4572,7 +4612,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4537797</v>
+        <v>4476895</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4581,77 +4621,93 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MLTP</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zabbar St Patr</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Red Star Paris</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4.27</v>
+        <v>2.24</v>
       </c>
       <c r="H37" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="J37" t="n">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="K37" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="M37" t="n">
         <v>1.74</v>
       </c>
       <c r="N37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+        <v>1.63</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R37" t="n">
+        <v>12.5</v>
+      </c>
       <c r="S37" t="n">
-        <v>4.64</v>
+        <v>2.81</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="W37" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="X37" t="n">
         <v>1.29</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.73</v>
+      </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
@@ -4679,7 +4735,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4476034</v>
+        <v>4476891</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4688,77 +4744,93 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BUL1</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cska Sofia</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2.06</v>
+        <v>2.76</v>
       </c>
       <c r="H38" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="J38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L38" t="n">
         <v>1.21</v>
       </c>
-      <c r="K38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.32</v>
-      </c>
       <c r="M38" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+        <v>1.93</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R38" t="n">
+        <v>20.55</v>
+      </c>
       <c r="S38" t="n">
-        <v>2.66</v>
+        <v>3.48</v>
       </c>
       <c r="T38" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U38" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="V38" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="W38" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="X38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
+        <v>2.83</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.55</v>
+      </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
@@ -4786,7 +4858,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4474505</v>
+        <v>4492357</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4795,92 +4867,92 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DAN</t>
+          <t>İS1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kopenhag</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odense</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="H39" t="n">
-        <v>4.66</v>
+        <v>3.02</v>
       </c>
       <c r="I39" t="n">
-        <v>6.48</v>
+        <v>3.67</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="M39" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="N39" t="n">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="O39" t="n">
-        <v>4.81</v>
+        <v>2.72</v>
       </c>
       <c r="P39" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="R39" t="n">
-        <v>7.11</v>
+        <v>19.85</v>
       </c>
       <c r="S39" t="n">
-        <v>1.61</v>
+        <v>2.32</v>
       </c>
       <c r="T39" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="U39" t="n">
-        <v>6.08</v>
+        <v>4.32</v>
       </c>
       <c r="V39" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="W39" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="X39" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.94</v>
+        <v>2.78</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.76</v>
+        <v>2.78</v>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>3.48</v>
       </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
@@ -4909,7 +4981,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4501635</v>
+        <v>4489939</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4918,92 +4990,92 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ROM</t>
+          <t>İN2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Universitatea C</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4.82</v>
+        <v>2.81</v>
       </c>
       <c r="H40" t="n">
-        <v>3.53</v>
+        <v>3.07</v>
       </c>
       <c r="I40" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="J40" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="K40" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="M40" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="N40" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.11</v>
+        <v>3.55</v>
       </c>
       <c r="P40" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.39</v>
+        <v>3.08</v>
       </c>
       <c r="R40" t="n">
-        <v>13.3</v>
+        <v>10.5</v>
       </c>
       <c r="S40" t="n">
-        <v>5.18</v>
+        <v>3.31</v>
       </c>
       <c r="T40" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="V40" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="W40" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="X40" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.03</v>
+        <v>3.38</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
@@ -5032,7 +5104,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4419081</v>
+        <v>4563358</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5041,66 +5113,66 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ARJPBM</t>
+          <t>EKV1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Urquiza</t>
+          <t>T.Universitari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.32</v>
+        <v>2.32</v>
       </c>
       <c r="H41" t="n">
-        <v>3.29</v>
+        <v>2.7</v>
       </c>
       <c r="I41" t="n">
-        <v>5.86</v>
+        <v>2.32</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="K41" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="L41" t="n">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="M41" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="N41" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>1.8</v>
+        <v>3.02</v>
       </c>
       <c r="T41" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="U41" t="n">
-        <v>6.22</v>
+        <v>3.04</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -5135,7 +5207,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4427051</v>
+        <v>4517332</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5144,92 +5216,88 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>İSÇ2</t>
+          <t>POR2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Amarante Fc</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="H42" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="I42" t="n">
-        <v>2.26</v>
+        <v>3.76</v>
       </c>
       <c r="J42" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>1.12</v>
       </c>
       <c r="L42" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="M42" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="N42" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="P42" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.07</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>10.45</v>
+        <v>18.35</v>
       </c>
       <c r="S42" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="T42" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="U42" t="n">
-        <v>2.79</v>
+        <v>4.37</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="W42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.18</v>
-      </c>
+        <v>1.55</v>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>3.39</v>
+        <v>2.65</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.39</v>
+        <v>3.15</v>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
@@ -5258,101 +5326,101 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4550147</v>
+        <v>4475906</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AŞMP</t>
+          <t>ARJ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Nassr (Riya</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Estudiantes Lp</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.14</v>
+        <v>2.35</v>
       </c>
       <c r="H43" t="n">
-        <v>4.7</v>
+        <v>2.76</v>
       </c>
       <c r="I43" t="n">
-        <v>7.01</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="L43" t="n">
-        <v>2.54</v>
+        <v>1.31</v>
       </c>
       <c r="M43" t="n">
-        <v>2.39</v>
+        <v>1.45</v>
       </c>
       <c r="N43" t="n">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>5.53</v>
+        <v>2.58</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.48</v>
+        <v>4.35</v>
       </c>
       <c r="R43" t="n">
-        <v>5.47</v>
+        <v>22.55</v>
       </c>
       <c r="S43" t="n">
-        <v>1.47</v>
+        <v>3.04</v>
       </c>
       <c r="T43" t="n">
-        <v>2.56</v>
+        <v>1.83</v>
       </c>
       <c r="U43" t="n">
-        <v>6.24</v>
+        <v>3.2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="W43" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="X43" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.73</v>
+        <v>2.91</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.87</v>
+        <v>2.64</v>
       </c>
       <c r="AA43" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>3.72</v>
       </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
@@ -5381,82 +5449,102 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4441272</v>
+        <v>4423346</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ARJPBN</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>D Belgrano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="H44" t="n">
-        <v>2.66</v>
+        <v>3.03</v>
       </c>
       <c r="I44" t="n">
-        <v>3.71</v>
+        <v>2.87</v>
       </c>
       <c r="J44" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="K44" t="n">
         <v>1.17</v>
       </c>
       <c r="L44" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+        <v>1.46</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R44" t="n">
+        <v>14.45</v>
+      </c>
       <c r="S44" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T44" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="U44" t="n">
-        <v>4.78</v>
+        <v>3.47</v>
       </c>
       <c r="V44" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="W44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
+        <v>1.83</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.52</v>
+      </c>
       <c r="Z44" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
+        <v>1.15</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.95</v>
+      </c>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
@@ -5484,101 +5572,97 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4542731</v>
+        <v>4454029</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TSL</t>
+          <t>BR2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>America Mineir</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1.95</v>
+        <v>3.09</v>
       </c>
       <c r="H45" t="n">
-        <v>3.38</v>
+        <v>2.91</v>
       </c>
       <c r="I45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R45" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
         <v>2.63</v>
       </c>
-      <c r="J45" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O45" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U45" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W45" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AA45" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
@@ -5607,102 +5691,86 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4517033</v>
+        <v>4435988</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ŞİL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Univ. De Şili</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Everton De Vina</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>7.22</v>
+        <v>1.42</v>
       </c>
       <c r="H46" t="n">
-        <v>4.25</v>
+        <v>3.43</v>
       </c>
       <c r="I46" t="n">
-        <v>1.23</v>
+        <v>4.17</v>
       </c>
       <c r="J46" t="n">
-        <v>2.57</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="N46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R46" t="n">
-        <v>12.9</v>
-      </c>
+        <v>1.42</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>7.02</v>
+        <v>1.85</v>
       </c>
       <c r="T46" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="U46" t="n">
-        <v>1.67</v>
+        <v>4.41</v>
       </c>
       <c r="V46" t="n">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="W46" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="X46" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.78</v>
-      </c>
+        <v>2.04</v>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
@@ -5730,101 +5798,101 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4535920</v>
+        <v>4423339</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>İTC</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Casarano</t>
+          <t>Atletico Mg</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1.8</v>
+        <v>1.17</v>
       </c>
       <c r="H47" t="n">
-        <v>2.89</v>
+        <v>4.89</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>7.87</v>
       </c>
       <c r="J47" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R47" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U47" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X47" t="n">
         <v>1.44</v>
       </c>
-      <c r="M47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="R47" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Y47" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.27</v>
+        <v>4.34</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
@@ -5853,102 +5921,68 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4535924</v>
+        <v>4560779</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>İTC</t>
+          <t>MEKKA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Atlas (K)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Puebla (K)</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2.81</v>
+        <v>1.21</v>
       </c>
       <c r="H48" t="n">
-        <v>2.97</v>
+        <v>4.27</v>
       </c>
       <c r="I48" t="n">
-        <v>1.85</v>
+        <v>5.73</v>
       </c>
       <c r="J48" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R48" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.64</v>
-      </c>
+        <v>2.26</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
@@ -5976,102 +6010,82 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4492791</v>
+        <v>4513978</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>İS2</t>
+          <t>KOL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fc Andorra</t>
+          <t>Jaguares</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="G49" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W49" t="n">
         <v>1.71</v>
       </c>
-      <c r="H49" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R49" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U49" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.07</v>
-      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
@@ -6099,86 +6113,102 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4537798</v>
+        <v>4454036</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MLTP</t>
+          <t>BR2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mosta Fc</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hibernians</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2.92</v>
+        <v>1.33</v>
       </c>
       <c r="H50" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="I50" t="n">
-        <v>1.74</v>
+        <v>5.21</v>
       </c>
       <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="R50" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W50" t="n">
         <v>1.48</v>
       </c>
-      <c r="K50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L50" t="n">
+      <c r="X50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1.13</v>
       </c>
-      <c r="M50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>2.88</v>
+      </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
@@ -6206,101 +6236,101 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4476895</v>
+        <v>4475907</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>ARJ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Instituto Cord</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star Paris</t>
+          <t>Riestra</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="H51" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="I51" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="J51" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="K51" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="L51" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="N51" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
-        <v>3.39</v>
+        <v>1.99</v>
       </c>
       <c r="P51" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.36</v>
+        <v>6.28</v>
       </c>
       <c r="R51" t="n">
-        <v>12.5</v>
+        <v>34.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="U51" t="n">
-        <v>3</v>
+        <v>4.88</v>
       </c>
       <c r="V51" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="W51" t="n">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="X51" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.4</v>
+        <v>3.69</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.44</v>
+        <v>2.05</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.73</v>
+        <v>5.53</v>
       </c>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
@@ -6329,102 +6359,82 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4476891</v>
+        <v>4513960</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>27.10.2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>04:05</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>KOL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2.76</v>
+        <v>1.64</v>
       </c>
       <c r="H52" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I52" t="n">
-        <v>2.08</v>
+        <v>3.53</v>
       </c>
       <c r="J52" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="K52" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="L52" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="M52" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="N52" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="R52" t="n">
-        <v>20.55</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="T52" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U52" t="n">
-        <v>2.76</v>
+        <v>4.16</v>
       </c>
       <c r="V52" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W52" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>3.55</v>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
@@ -6450,1610 +6460,6 @@
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="inlineStr"/>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>4492357</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>İS1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H53" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O53" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U53" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr"/>
-      <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>4489939</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>İN2</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Walsall</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Salford City</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H54" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O54" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R54" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
-      <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr"/>
-      <c r="AS54" t="inlineStr"/>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="inlineStr"/>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
-      <c r="BA54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>4563358</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>EKV1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>T.Universitari</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U55" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
-      <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="inlineStr"/>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="inlineStr"/>
-      <c r="AV55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr"/>
-      <c r="AX55" t="inlineStr"/>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr"/>
-      <c r="BA55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>4517332</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>23:45</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>POR2</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Torreense</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Amarante Fc</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R56" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U56" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
-      <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="inlineStr"/>
-      <c r="AV56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr"/>
-      <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>4475906</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>ARJ</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Union Santa Fe</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Estudiantes Lp</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H57" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R57" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U57" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="inlineStr"/>
-      <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="inlineStr"/>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AU57" t="inlineStr"/>
-      <c r="AV57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr"/>
-      <c r="AX57" t="inlineStr"/>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr"/>
-      <c r="BA57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>4423346</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BR1</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Gremio</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="R58" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U58" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X58" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
-      <c r="AQ58" t="inlineStr"/>
-      <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="inlineStr"/>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AU58" t="inlineStr"/>
-      <c r="AV58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr"/>
-      <c r="AX58" t="inlineStr"/>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr"/>
-      <c r="BA58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>4454029</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>BR2</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>America Mineir</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Cuiaba</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O59" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R59" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U59" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
-      <c r="AR59" t="inlineStr"/>
-      <c r="AS59" t="inlineStr"/>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr"/>
-      <c r="AV59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr"/>
-      <c r="AX59" t="inlineStr"/>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr"/>
-      <c r="BA59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>4435988</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ŞİL</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Univ. De Şili</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Everton De Vina</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H60" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="I60" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T60" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U60" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X60" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr"/>
-      <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="inlineStr"/>
-      <c r="AQ60" t="inlineStr"/>
-      <c r="AR60" t="inlineStr"/>
-      <c r="AS60" t="inlineStr"/>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AU60" t="inlineStr"/>
-      <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr"/>
-      <c r="AX60" t="inlineStr"/>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr"/>
-      <c r="BA60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>4423339</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BR1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Atletico Mg</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="I61" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O61" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R61" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="S61" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U61" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="inlineStr"/>
-      <c r="AR61" t="inlineStr"/>
-      <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="inlineStr"/>
-      <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
-      <c r="AX61" t="inlineStr"/>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr"/>
-      <c r="BA61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>4560779</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>MEKKA</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Atlas (K)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Puebla (K)</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H62" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="I62" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
-      <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr"/>
-      <c r="AP62" t="inlineStr"/>
-      <c r="AQ62" t="inlineStr"/>
-      <c r="AR62" t="inlineStr"/>
-      <c r="AS62" t="inlineStr"/>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AU62" t="inlineStr"/>
-      <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="inlineStr"/>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr"/>
-      <c r="BA62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>4513978</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>KOL</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Jaguares</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Llaneros</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U63" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr"/>
-      <c r="AP63" t="inlineStr"/>
-      <c r="AQ63" t="inlineStr"/>
-      <c r="AR63" t="inlineStr"/>
-      <c r="AS63" t="inlineStr"/>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AU63" t="inlineStr"/>
-      <c r="AV63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr"/>
-      <c r="AX63" t="inlineStr"/>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr"/>
-      <c r="BA63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>4454036</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BR2</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H64" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I64" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L64" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R64" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T64" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U64" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD64" t="inlineStr"/>
-      <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
-      <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="inlineStr"/>
-      <c r="AO64" t="inlineStr"/>
-      <c r="AP64" t="inlineStr"/>
-      <c r="AQ64" t="inlineStr"/>
-      <c r="AR64" t="inlineStr"/>
-      <c r="AS64" t="inlineStr"/>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AU64" t="inlineStr"/>
-      <c r="AV64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr"/>
-      <c r="AX64" t="inlineStr"/>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr"/>
-      <c r="BA64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>4475907</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>ARJ</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Instituto Cord</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Riestra</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I65" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L65" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="R65" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U65" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="V65" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X65" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="AD65" t="inlineStr"/>
-      <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="inlineStr"/>
-      <c r="AO65" t="inlineStr"/>
-      <c r="AP65" t="inlineStr"/>
-      <c r="AQ65" t="inlineStr"/>
-      <c r="AR65" t="inlineStr"/>
-      <c r="AS65" t="inlineStr"/>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AU65" t="inlineStr"/>
-      <c r="AV65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr"/>
-      <c r="AX65" t="inlineStr"/>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr"/>
-      <c r="BA65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>4513960</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>04:05</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>KOL</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Bucaramanga</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I66" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L66" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T66" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U66" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr"/>
-      <c r="AO66" t="inlineStr"/>
-      <c r="AP66" t="inlineStr"/>
-      <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="inlineStr"/>
-      <c r="AS66" t="inlineStr"/>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AU66" t="inlineStr"/>
-      <c r="AV66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr"/>
-      <c r="AX66" t="inlineStr"/>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr"/>
-      <c r="BA66" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/oranlar_yaklasan.xlsx
+++ b/oranlar_yaklasan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA4"/>
+  <dimension ref="A1:BA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,355 +682,6 @@
           <t>Skor</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>4454036</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BR2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4475907</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ARJ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Instituto Cord</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Riestra</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="R3" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4513960</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>27.10.2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>04:05</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KOL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bucaramanga</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
